--- a/uploads/Book1.xlsx
+++ b/uploads/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Hujjatlar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905DEB06-075F-4F5A-B9FC-219E20B2014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2457FA-C0BF-4FBC-8987-AB1FC2223476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6E611357-18FA-44DC-A111-E85758824845}"/>
   </bookViews>
@@ -25,88 +25,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Mahsulot turi</t>
   </si>
   <si>
+    <t>Rasmi</t>
+  </si>
+  <si>
+    <t>Televizor</t>
+  </si>
+  <si>
+    <t>Brendi</t>
+  </si>
+  <si>
+    <t>Tannarx</t>
+  </si>
+  <si>
+    <t>https://images.uzum.uz/d6tqnoq1146ojv97mrtg/t_product_540_high.jpg</t>
+  </si>
+  <si>
+    <t>32 H4101 (Стальной) HD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Телевизоры (32) ARTEL </t>
+  </si>
+  <si>
     <t>Mahsulot nomi</t>
-  </si>
-  <si>
-    <t>Rasmi</t>
-  </si>
-  <si>
-    <t>Narxi</t>
-  </si>
-  <si>
-    <t>Muddati</t>
-  </si>
-  <si>
-    <t>Oylik to'lovi</t>
-  </si>
-  <si>
-    <t>Tartib</t>
-  </si>
-  <si>
-    <t>Televizor</t>
-  </si>
-  <si>
-    <t>Telefon</t>
-  </si>
-  <si>
-    <t>https://macbro.uz/cdn/shop/files/samsung_s_26_ultra_black_1.png?v=1772282600</t>
-  </si>
-  <si>
-    <t>https://prod-cdn.prod.asbis.io/s3/cms/product/41/49/4149198f1713e718ba920b85acffb4f4/250915140038367093.webp</t>
-  </si>
-  <si>
-    <t>Samsung S26 ultra 12/256</t>
-  </si>
-  <si>
-    <t>Iphone 17 pro max, 16/1TB</t>
-  </si>
-  <si>
-    <t>Muzlatgich</t>
-  </si>
-  <si>
-    <t>https://cdn.mediapark.uz/imgs/9c67af0b-0166-4c50-9c75-90f37e888ccb_Artboard-1.webp</t>
-  </si>
-  <si>
-    <t>Konditsioner</t>
-  </si>
-  <si>
-    <t>https://cdn.mediapark.uz/imgs/991470c3-e565-446c-8ded-5621e6e20dd5_Artboard-1.webp</t>
-  </si>
-  <si>
-    <t>8 109 000</t>
-  </si>
-  <si>
-    <t>Notebook</t>
-  </si>
-  <si>
-    <t>https://technochain.uz/api/app/project_files/product_img/b5e18de1-Asus%20Zenbook%20A14%20OLED%20UX3407RA%20(2).png</t>
-  </si>
-  <si>
-    <t>Asus Zenbook A14 OLED UX3407RA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMSUNG RB31FERNDSA/UZ </t>
-  </si>
-  <si>
-    <t>Artel ICEBERG 18BE INVERTER</t>
-  </si>
-  <si>
-    <t>LG 55NANO81A6A 4K UltraHD</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/B6CBxFXF/11-Zakat.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,16 +74,75 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -139,17 +150,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Calculation" xfId="2" builtinId="22"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -463,185 +514,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1EBB2A-6180-4078-B361-8F51BA8090BC}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="130.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="160.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2">
-        <v>945000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2">
-        <v>18000000</v>
-      </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2">
-        <v>8745000</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1890000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2">
-        <v>6200000</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="2">
-        <v>16470000</v>
-      </c>
-      <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1625000</v>
-      </c>
-    </row>
+      <c r="E2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C49" s="5"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C50" s="5"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C51" s="5"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C52" s="5"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C53" s="5"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C54" s="5"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C55" s="5"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="4"/>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D57" t="str">
+        <f t="shared" ref="D57" si="0">C57&amp;" "&amp;B63</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D60" t="str">
+        <f>C60&amp;" "&amp;B66</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D61" t="str">
+        <f t="shared" ref="D61:D63" si="1">C61&amp;" "&amp;B67</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D62" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="63" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D63" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{22657FA8-8F92-4049-AB8B-36EB74C349E4}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{210CE23D-58DA-44E3-829F-D6D7654779A4}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{F0B75538-95D7-4922-80B5-0CBF3EA9BACC}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{C87F8C8F-53C6-4ED9-BD89-B1CBBE8FBBED}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{8518187A-228F-4AE8-ADC6-9AA849FD670D}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{C0837657-8DC9-490E-8E1A-2D9A87F07C60}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{4866E0E1-EA95-4F1E-915C-671B3E88547E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
